--- a/resources/templates/standard/L1200-05.xlsx
+++ b/resources/templates/standard/L1200-05.xlsx
@@ -11,7 +11,10 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="23" uniqueCount="23">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="24">
+  <si>
+    <t>{{companyLogo}}</t>
+  </si>
   <si>
     <t xml:space="preserve">지그 및 치공구
 검사 성적서</t>
@@ -578,12 +581,14 @@
   </cols>
   <sheetData>
     <row r="1" ht="20.1" customHeight="1" spans="1:33" x14ac:dyDescent="0.25">
-      <c r="A1" s="1"/>
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
       <c r="D1" s="1"/>
       <c r="E1" s="2" t="s">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F1" s="2"/>
       <c r="G1" s="2"/>
@@ -600,26 +605,26 @@
       <c r="R1" s="2"/>
       <c r="S1" s="2"/>
       <c r="T1" s="3" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="U1" s="3"/>
       <c r="V1" s="4" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="W1" s="4"/>
       <c r="X1" s="4"/>
       <c r="Y1" s="4" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="Z1" s="4"/>
       <c r="AA1" s="4"/>
       <c r="AB1" s="4" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AC1" s="4"/>
       <c r="AD1" s="4"/>
       <c r="AE1" s="4" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AF1" s="4"/>
       <c r="AG1" s="4"/>
@@ -696,7 +701,7 @@
     </row>
     <row r="4" ht="20.1" customHeight="1" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A4" s="6" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B4" s="6"/>
       <c r="C4" s="6"/>
@@ -709,7 +714,7 @@
       <c r="J4" s="7"/>
       <c r="K4" s="7"/>
       <c r="L4" s="8" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="M4" s="8"/>
       <c r="N4" s="8"/>
@@ -722,7 +727,7 @@
       <c r="U4" s="7"/>
       <c r="V4" s="7"/>
       <c r="W4" s="8" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="X4" s="8"/>
       <c r="Y4" s="8"/>
@@ -737,7 +742,7 @@
     </row>
     <row r="5" ht="20.1" customHeight="1" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A5" s="9" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B5" s="9"/>
       <c r="C5" s="9"/>
@@ -750,7 +755,7 @@
       <c r="J5" s="5"/>
       <c r="K5" s="5"/>
       <c r="L5" s="10" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="M5" s="10"/>
       <c r="N5" s="10"/>
@@ -763,7 +768,7 @@
       <c r="U5" s="5"/>
       <c r="V5" s="5"/>
       <c r="W5" s="10" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="X5" s="10"/>
       <c r="Y5" s="10"/>
@@ -778,7 +783,7 @@
     </row>
     <row r="6" ht="20.1" customHeight="1" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A6" s="9" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B6" s="9"/>
       <c r="C6" s="9"/>
@@ -791,7 +796,7 @@
       <c r="J6" s="5"/>
       <c r="K6" s="5"/>
       <c r="L6" s="10" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="M6" s="10"/>
       <c r="N6" s="10"/>
@@ -804,7 +809,7 @@
       <c r="U6" s="5"/>
       <c r="V6" s="5"/>
       <c r="W6" s="10" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="X6" s="10"/>
       <c r="Y6" s="10"/>
@@ -819,7 +824,7 @@
     </row>
     <row r="7" ht="20.1" customHeight="1" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A7" s="11" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B7" s="11"/>
       <c r="C7" s="11"/>
@@ -856,7 +861,7 @@
     </row>
     <row r="8" ht="20.1" customHeight="1" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A8" s="12" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B8" s="12"/>
       <c r="C8" s="12"/>
@@ -1313,11 +1318,11 @@
     </row>
     <row r="21" ht="20.1" customHeight="1" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A21" s="9" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B21" s="9"/>
       <c r="C21" s="10" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="D21" s="10"/>
       <c r="E21" s="10"/>
@@ -1329,7 +1334,7 @@
       <c r="K21" s="10"/>
       <c r="L21" s="10"/>
       <c r="M21" s="10" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="N21" s="10"/>
       <c r="O21" s="10"/>
@@ -1341,7 +1346,7 @@
       <c r="U21" s="10"/>
       <c r="V21" s="10"/>
       <c r="W21" s="10" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="X21" s="10"/>
       <c r="Y21" s="10"/>
@@ -1349,7 +1354,7 @@
       <c r="AA21" s="10"/>
       <c r="AB21" s="10"/>
       <c r="AC21" s="10" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AD21" s="10"/>
       <c r="AE21" s="10"/>
@@ -1743,7 +1748,7 @@
     </row>
     <row r="33" ht="20.1" customHeight="1" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A33" s="14" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B33" s="14"/>
       <c r="C33" s="5"/>
